--- a/diseases/d234/2000-2004.xlsx
+++ b/diseases/d234/2000-2004.xlsx
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13938,7 +13938,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16944,7 +16944,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18447,7 +18447,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19950,7 +19950,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24459,7 +24459,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -25962,7 +25962,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -28968,7 +28968,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -30471,7 +30471,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -31974,7 +31974,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -33477,7 +33477,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -34980,7 +34980,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -36483,7 +36483,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -37986,7 +37986,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -39489,7 +39489,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -40992,7 +40992,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -42495,7 +42495,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -43998,7 +43998,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -45501,7 +45501,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -47004,7 +47004,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -48507,7 +48507,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -50010,7 +50010,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -51513,7 +51513,7 @@
       </c>
       <c r="AM273" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN273" t="b">
@@ -53016,7 +53016,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -54519,7 +54519,7 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -56170,7 +56170,7 @@
       </c>
       <c r="AM298" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN298" t="b">
@@ -57821,7 +57821,7 @@
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN307" t="b">
@@ -59472,7 +59472,7 @@
       </c>
       <c r="AM316" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN316" t="b">
@@ -60975,7 +60975,7 @@
       </c>
       <c r="AM324" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN324" t="b">
@@ -62478,7 +62478,7 @@
       </c>
       <c r="AM332" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN332" t="b">
@@ -64129,7 +64129,7 @@
       </c>
       <c r="AM341" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN341" t="b">
@@ -65780,7 +65780,7 @@
       </c>
       <c r="AM350" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN350" t="b">
@@ -67431,7 +67431,7 @@
       </c>
       <c r="AM359" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN359" t="b">
@@ -69082,7 +69082,7 @@
       </c>
       <c r="AM368" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN368" t="b">
@@ -70733,7 +70733,7 @@
       </c>
       <c r="AM377" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN377" t="b">
@@ -72236,7 +72236,7 @@
       </c>
       <c r="AM385" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN385" t="b">
@@ -73739,7 +73739,7 @@
       </c>
       <c r="AM393" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN393" t="b">
@@ -75242,7 +75242,7 @@
       </c>
       <c r="AM401" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN401" t="b">
@@ -76893,7 +76893,7 @@
       </c>
       <c r="AM410" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN410" t="b">
@@ -78544,7 +78544,7 @@
       </c>
       <c r="AM419" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN419" t="b">
@@ -80195,7 +80195,7 @@
       </c>
       <c r="AM428" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN428" t="b">
@@ -81846,7 +81846,7 @@
       </c>
       <c r="AM437" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN437" t="b">
@@ -83497,7 +83497,7 @@
       </c>
       <c r="AM446" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN446" t="b">
@@ -85148,7 +85148,7 @@
       </c>
       <c r="AM455" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN455" t="b">
@@ -86799,7 +86799,7 @@
       </c>
       <c r="AM464" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN464" t="b">
@@ -88450,7 +88450,7 @@
       </c>
       <c r="AM473" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN473" t="b">
